--- a/TEngine/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62A34ABB-3724-4DD9-97BC-F6E55CBD4FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB871587-1F16-437A-8B8C-8CE3ECB849C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -138,6 +138,18 @@
   </si>
   <si>
     <t>多语言key|LanguageContent@Language.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>level.TbLevel</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ConfLevel</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡|Level@Level.xlsx</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -145,7 +157,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -175,6 +187,15 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -199,15 +220,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -217,9 +241,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="2" builtinId="8"/>
     <cellStyle name="好" xfId="1" builtinId="26"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -493,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
@@ -635,11 +663,26 @@
         <v>35</v>
       </c>
     </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="E5" r:id="rId1" xr:uid="{F8331D80-79B5-4C3D-A8DC-C0FBC0F2DDAD}"/>
     <hyperlink ref="E6" r:id="rId2" xr:uid="{5E7AAD33-5E4C-4555-9C21-BA1ED5240838}"/>
+    <hyperlink ref="E7" r:id="rId3" xr:uid="{74C3DEC5-621F-4C88-B4E6-6422D1682670}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/TEngine/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB871587-1F16-437A-8B8C-8CE3ECB849C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03B962F-417D-4EE2-87A4-79F3947D5596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
   <si>
     <t>##var</t>
   </si>
@@ -150,6 +150,18 @@
   </si>
   <si>
     <t>关卡|Level@Level.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>reward.TbReward</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ConfReward</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reward.xlsx</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -521,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
@@ -677,6 +689,20 @@
         <v>38</v>
       </c>
     </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
